--- a/data/trans_orig/IP16A112_2023R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A112_2023R-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27757</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>32004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45585</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>47156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34556</t>
+          <t>34663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74777</t>
+          <t>74794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16620</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55986</t>
+          <t>55813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>37112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90723</t>
+          <t>86893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12968</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19674</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>33805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,5%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17177</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21878</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25741</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28643</t>
+          <t>28579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>17098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45497</t>
+          <t>45561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>44851</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90425</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69163</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>92577</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114202</t>
+          <t>118007</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>172312</t>
+          <t>172866</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88927</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135855</t>
+          <t>134501</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88766</t>
+          <t>90132</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>113546</t>
+          <t>114756</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>189749</t>
+          <t>189195</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>247859</t>
+          <t>244054</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
